--- a/testdata/Opencart_LoginData.xlsx
+++ b/testdata/Opencart_LoginData.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A52F22-9587-4E6A-99CE-BCAD45217605}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C794EED8-493F-4F19-BE73-4F20BB6A116A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-100" yWindow="-100" windowWidth="21467" windowHeight="11576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -49,21 +49,21 @@
     <t>pavan@gmail.com</t>
   </si>
   <si>
-    <t>sultan789@gmail.com</t>
-  </si>
-  <si>
     <t>Hornet@6944</t>
+  </si>
+  <si>
+    <t>sultansaudagar503@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Mangal"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -71,7 +71,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Mangal"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -79,14 +79,14 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Mangal"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Mangal"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -460,14 +460,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.25" customWidth="1"/>
-    <col min="2" max="2" width="23.125" customWidth="1"/>
+    <col min="1" max="1" width="30.19921875" customWidth="1"/>
+    <col min="2" max="2" width="23.09765625" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18">
+    <row r="1" spans="1:3" ht="18.3" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -478,18 +478,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18">
+    <row r="2" spans="1:3" ht="18.3" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18">
+    <row r="3" spans="1:3" ht="18.3" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -500,7 +500,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18">
+    <row r="4" spans="1:3" ht="18.3" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
@@ -511,7 +511,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="24.75" customHeight="1">
+    <row r="5" spans="1:3" ht="24.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
